--- a/Pimary VS Secondary.xlsx
+++ b/Pimary VS Secondary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8E16A5B-3F94-4DFA-8B3D-720A7A4AEA10}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C6DBA0-585F-4DD1-A31D-3D805183713D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{B13BB3DE-45F3-4A08-8C5B-C8EF34D5413B}"/>
   </bookViews>
@@ -25,10 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
-  <si>
-    <t>Stock In Hand (Primary)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -60,31 +57,52 @@
     <t>Chicken Chatkhara  (ECO)</t>
   </si>
   <si>
-    <t>Total</t>
-  </si>
-  <si>
     <t>Opening</t>
   </si>
   <si>
-    <t>Opening (Ctn)</t>
-  </si>
-  <si>
-    <t>Total Warehouse</t>
-  </si>
-  <si>
-    <t>18/07/26</t>
-  </si>
-  <si>
     <t xml:space="preserve">Expired </t>
   </si>
   <si>
-    <t>Stock In Hand</t>
-  </si>
-  <si>
-    <t>Warehouse</t>
-  </si>
-  <si>
     <t>Diffrence</t>
+  </si>
+  <si>
+    <t>Warehouse InHand</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Primary Stock </t>
+  </si>
+  <si>
+    <t>In Hand</t>
+  </si>
+  <si>
+    <t>Sale MTD</t>
+  </si>
+  <si>
+    <t>EXP</t>
+  </si>
+  <si>
+    <t>Total Pcs</t>
+  </si>
+  <si>
+    <t>Ctn's</t>
+  </si>
+  <si>
+    <t>Stock Expected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monthly Sales &amp; Inventory Report </t>
+  </si>
+  <si>
+    <t>s</t>
+  </si>
+  <si>
+    <t>Til 23rd</t>
+  </si>
+  <si>
+    <t>Total Primary WH</t>
+  </si>
+  <si>
+    <t>18/7/26</t>
   </si>
 </sst>
 </file>
@@ -95,7 +113,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -120,13 +138,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="18"/>
       <color theme="1"/>
@@ -157,8 +168,54 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Book Antiqua"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Book Antiqua"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Book Antiqua"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Book Antiqua"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Book Antiqua"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <color theme="1"/>
+      <name val="Book Antiqua"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Book Antiqua"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -189,8 +246,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="4">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -213,86 +282,80 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -609,397 +672,468 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C4897FB-F3E4-4933-BDE3-BEDB17D2ED6F}">
-  <dimension ref="C5:O17"/>
+  <dimension ref="B5:N20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="38.6328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.54296875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="13.81640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="24.6328125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.90625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="19.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.81640625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="13.7265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.1796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="44.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7265625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.6328125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.54296875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.54296875" customWidth="1"/>
+    <col min="12" max="12" width="31.453125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.90625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="3:15" ht="19" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="D5" s="20" t="s">
+    <row r="5" spans="2:14" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="D5" s="10" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="10"/>
+      <c r="F5" s="10"/>
+      <c r="G5" s="10"/>
+      <c r="H5" s="10"/>
+      <c r="I5" s="10"/>
+      <c r="J5" s="10"/>
+      <c r="K5" s="10"/>
+      <c r="L5" s="10"/>
+      <c r="M5" s="10"/>
+      <c r="N5" s="10"/>
+    </row>
+    <row r="6" spans="2:14" ht="30.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="C6" s="9"/>
+      <c r="D6" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="E5" s="20"/>
-      <c r="F5" s="20"/>
-      <c r="G5" s="20"/>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="20"/>
-      <c r="O5" s="20"/>
-    </row>
-    <row r="6" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="C6" s="13"/>
-      <c r="D6" s="14" t="s">
+      <c r="E6" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="E6" s="14" t="s">
+      <c r="F6" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="G6" s="19">
+        <v>46029</v>
+      </c>
+      <c r="H6" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I6" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="F6" s="14" t="s">
+      <c r="K6" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="L6" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="M6" s="12" t="s">
         <v>12</v>
       </c>
-      <c r="G6" s="14" t="s">
-        <v>13</v>
-      </c>
-      <c r="H6" s="15">
-        <v>46029</v>
-      </c>
-      <c r="I6" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="J6" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="K6" s="14" t="s">
+      <c r="N6" s="12" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="2:14" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="D7" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="14" t="s">
-        <v>17</v>
-      </c>
-      <c r="M6" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="N6" s="14" t="s">
-        <v>19</v>
-      </c>
-      <c r="O6" s="14" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="7" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="2">
+        <v>70</v>
+      </c>
+      <c r="F7" s="4">
+        <v>9586</v>
+      </c>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21">
+        <f>300*40</f>
+        <v>12000</v>
+      </c>
+      <c r="I7" s="22">
+        <f t="shared" ref="I7:I13" si="0">F7+G7+H7</f>
+        <v>21586</v>
+      </c>
+      <c r="J7" s="5">
+        <v>11967</v>
+      </c>
+      <c r="K7" s="23">
+        <f>I7-J7</f>
+        <v>9619</v>
+      </c>
+      <c r="L7" s="24">
+        <v>9710</v>
+      </c>
+      <c r="M7" s="8">
+        <f>L7-K7</f>
+        <v>91</v>
+      </c>
+      <c r="N7" s="7">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="8" spans="2:14" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="D8" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E8" s="2">
         <v>70</v>
       </c>
-      <c r="F7" s="7">
-        <v>9586</v>
-      </c>
-      <c r="G7" s="6">
-        <f>F7/40</f>
-        <v>239.65</v>
-      </c>
-      <c r="H7" s="8"/>
-      <c r="I7" s="8">
-        <v>300</v>
-      </c>
-      <c r="J7" s="9">
-        <f t="shared" ref="J7:J13" si="0">G7+H7+I7</f>
-        <v>539.65</v>
-      </c>
-      <c r="K7" s="11">
-        <v>284.625</v>
-      </c>
-      <c r="L7" s="10">
-        <f t="shared" ref="L7:L13" si="1">J7-K7</f>
-        <v>255.02499999999998</v>
-      </c>
-      <c r="M7" s="16"/>
-      <c r="N7" s="19">
-        <f>L7-M7</f>
-        <v>255.02499999999998</v>
-      </c>
-      <c r="O7" s="17">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="8" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="D8" s="1" t="s">
+      <c r="F8" s="4">
+        <v>10668</v>
+      </c>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21">
+        <f>200*40</f>
+        <v>8000</v>
+      </c>
+      <c r="I8" s="22">
+        <f t="shared" si="0"/>
+        <v>18668</v>
+      </c>
+      <c r="J8" s="5">
+        <v>11897</v>
+      </c>
+      <c r="K8" s="23">
+        <f t="shared" ref="K8:K13" si="1">I8-J8</f>
+        <v>6771</v>
+      </c>
+      <c r="L8" s="24">
+        <v>6906</v>
+      </c>
+      <c r="M8" s="8">
+        <f t="shared" ref="M8:M13" si="2">L8-K8</f>
+        <v>135</v>
+      </c>
+      <c r="N8" s="7">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="9" spans="2:14" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="B9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E9" s="2">
         <v>70</v>
       </c>
-      <c r="F8" s="7">
-        <v>10668</v>
-      </c>
-      <c r="G8" s="6">
-        <f t="shared" ref="G8:G14" si="2">F8/40</f>
-        <v>266.7</v>
-      </c>
-      <c r="H8" s="8"/>
-      <c r="I8" s="8">
-        <v>200</v>
-      </c>
-      <c r="J8" s="9">
+      <c r="F9" s="4"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="22">
         <f t="shared" si="0"/>
-        <v>466.7</v>
-      </c>
-      <c r="K8" s="11">
-        <v>284.35000000000002</v>
-      </c>
-      <c r="L8" s="10">
+        <v>0</v>
+      </c>
+      <c r="J9" s="5"/>
+      <c r="K9" s="23">
         <f t="shared" si="1"/>
-        <v>182.34999999999997</v>
-      </c>
-      <c r="M8" s="16"/>
-      <c r="N8" s="19">
-        <f t="shared" ref="N8:N13" si="3">L8-M8</f>
-        <v>182.34999999999997</v>
-      </c>
-      <c r="O8" s="17">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="9" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="D9" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="4">
-        <v>70</v>
-      </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="6">
+        <v>0</v>
+      </c>
+      <c r="L9" s="24"/>
+      <c r="M9" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="H9" s="8"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="9">
+      <c r="N9" s="7">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="10" spans="2:14" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="D10" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="E10" s="2">
+        <v>120</v>
+      </c>
+      <c r="F10" s="4">
+        <v>10905</v>
+      </c>
+      <c r="G10" s="21">
+        <f>750*40</f>
+        <v>30000</v>
+      </c>
+      <c r="H10" s="21"/>
+      <c r="I10" s="22">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="K9" s="11">
-        <v>0</v>
-      </c>
-      <c r="L9" s="10">
+        <v>40905</v>
+      </c>
+      <c r="J10" s="5">
+        <v>22476</v>
+      </c>
+      <c r="K10" s="23">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="M9" s="16"/>
-      <c r="N9" s="19">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="O9" s="17">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="10" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="D10" s="1" t="s">
+        <v>18429</v>
+      </c>
+      <c r="L10" s="24">
+        <v>18826</v>
+      </c>
+      <c r="M10" s="8">
+        <f t="shared" si="2"/>
+        <v>397</v>
+      </c>
+      <c r="N10" s="7">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="2:14" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="D11" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E11" s="2">
         <v>120</v>
       </c>
-      <c r="F10" s="7">
-        <v>10905</v>
-      </c>
-      <c r="G10" s="6">
+      <c r="F11" s="4">
+        <v>5595</v>
+      </c>
+      <c r="G11" s="21">
+        <f>203*40</f>
+        <v>8120</v>
+      </c>
+      <c r="H11" s="21"/>
+      <c r="I11" s="22">
+        <f t="shared" si="0"/>
+        <v>13715</v>
+      </c>
+      <c r="J11" s="5">
+        <v>16904</v>
+      </c>
+      <c r="K11" s="23">
+        <f t="shared" si="1"/>
+        <v>-3189</v>
+      </c>
+      <c r="L11" s="24">
+        <v>12836</v>
+      </c>
+      <c r="M11" s="8">
         <f t="shared" si="2"/>
-        <v>272.625</v>
-      </c>
-      <c r="H10" s="8">
-        <v>750</v>
-      </c>
-      <c r="I10" s="8"/>
-      <c r="J10" s="9">
+        <v>16025</v>
+      </c>
+      <c r="N11" s="7">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="12" spans="2:14" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="D12" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="E12" s="2">
+        <v>120</v>
+      </c>
+      <c r="F12" s="4">
+        <v>7110</v>
+      </c>
+      <c r="G12" s="21">
+        <f>1047*40</f>
+        <v>41880</v>
+      </c>
+      <c r="H12" s="21">
+        <f>400*40</f>
+        <v>16000</v>
+      </c>
+      <c r="I12" s="22">
         <f t="shared" si="0"/>
-        <v>1022.625</v>
-      </c>
-      <c r="K10" s="11">
-        <v>548.25</v>
-      </c>
-      <c r="L10" s="10">
+        <v>64990</v>
+      </c>
+      <c r="J12" s="5">
+        <v>27279</v>
+      </c>
+      <c r="K12" s="23">
         <f t="shared" si="1"/>
-        <v>474.375</v>
-      </c>
-      <c r="M10" s="16"/>
-      <c r="N10" s="19">
-        <f t="shared" si="3"/>
-        <v>474.375</v>
-      </c>
-      <c r="O10" s="17">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="D11" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="4">
-        <v>120</v>
-      </c>
-      <c r="F11" s="7">
-        <v>5595</v>
-      </c>
-      <c r="G11" s="6">
+        <v>37711</v>
+      </c>
+      <c r="L12" s="24">
+        <v>22468</v>
+      </c>
+      <c r="M12" s="8">
         <f t="shared" si="2"/>
-        <v>139.875</v>
-      </c>
-      <c r="H11" s="8">
-        <v>203</v>
-      </c>
-      <c r="I11" s="8"/>
-      <c r="J11" s="9">
+        <v>-15243</v>
+      </c>
+      <c r="N12" s="7">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="2:14" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="D13" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E13" s="2">
+        <v>60</v>
+      </c>
+      <c r="F13" s="4">
+        <v>66124</v>
+      </c>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="22">
         <f t="shared" si="0"/>
-        <v>342.875</v>
-      </c>
-      <c r="K11" s="11">
-        <v>405.40000000000003</v>
-      </c>
-      <c r="L11" s="10">
+        <v>66124</v>
+      </c>
+      <c r="J13" s="5">
+        <v>18330</v>
+      </c>
+      <c r="K13" s="23">
         <f t="shared" si="1"/>
-        <v>-62.525000000000034</v>
-      </c>
-      <c r="M11" s="16"/>
-      <c r="N11" s="19">
-        <f t="shared" si="3"/>
-        <v>-62.525000000000034</v>
-      </c>
-      <c r="O11" s="17">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="12" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="D12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" s="4">
-        <v>120</v>
-      </c>
-      <c r="F12" s="7">
-        <v>7110</v>
-      </c>
-      <c r="G12" s="6">
+        <v>47794</v>
+      </c>
+      <c r="L13" s="24">
+        <v>48173</v>
+      </c>
+      <c r="M13" s="8">
         <f t="shared" si="2"/>
-        <v>177.75</v>
-      </c>
-      <c r="H12" s="8">
-        <v>1047</v>
-      </c>
-      <c r="I12" s="8">
-        <v>400</v>
-      </c>
-      <c r="J12" s="9">
-        <f t="shared" si="0"/>
-        <v>1624.75</v>
-      </c>
-      <c r="K12" s="11">
-        <v>647.43500000000006</v>
-      </c>
-      <c r="L12" s="10">
-        <f t="shared" si="1"/>
-        <v>977.31499999999994</v>
-      </c>
-      <c r="M12" s="16"/>
-      <c r="N12" s="19">
-        <f t="shared" si="3"/>
-        <v>977.31499999999994</v>
-      </c>
-      <c r="O12" s="17">
+        <v>379</v>
+      </c>
+      <c r="N13" s="7">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="2:14" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D14" s="12" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="13" spans="3:15" ht="23.5" x14ac:dyDescent="0.55000000000000004">
-      <c r="D13" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E13" s="4">
-        <v>60</v>
-      </c>
-      <c r="F13" s="7">
-        <v>66124</v>
-      </c>
-      <c r="G13" s="6">
-        <f t="shared" si="2"/>
-        <v>1653.1</v>
-      </c>
-      <c r="H13" s="8"/>
-      <c r="I13" s="8"/>
-      <c r="J13" s="9">
-        <f t="shared" si="0"/>
-        <v>1653.1</v>
-      </c>
-      <c r="K13" s="11">
-        <v>444.37999999999994</v>
-      </c>
-      <c r="L13" s="10">
-        <f t="shared" si="1"/>
-        <v>1208.72</v>
-      </c>
-      <c r="M13" s="16"/>
-      <c r="N13" s="19">
-        <f t="shared" si="3"/>
-        <v>1208.72</v>
-      </c>
-      <c r="O13" s="17">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="14" spans="3:15" ht="29.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="D14" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E14" s="2"/>
-      <c r="F14" s="5">
+      <c r="E14" s="13"/>
+      <c r="F14" s="3">
         <f>SUM(F7:F13)</f>
         <v>109988</v>
       </c>
-      <c r="G14" s="5">
-        <f t="shared" si="2"/>
+      <c r="G14" s="6">
+        <f>SUM(G7:G13)</f>
+        <v>80000</v>
+      </c>
+      <c r="H14" s="6">
+        <f t="shared" ref="H14:N14" si="3">SUM(H7:H13)</f>
+        <v>36000</v>
+      </c>
+      <c r="I14" s="6">
+        <f t="shared" si="3"/>
+        <v>225988</v>
+      </c>
+      <c r="J14" s="6">
+        <f t="shared" si="3"/>
+        <v>108853</v>
+      </c>
+      <c r="K14" s="6">
+        <f t="shared" si="3"/>
+        <v>117135</v>
+      </c>
+      <c r="L14" s="6">
+        <f t="shared" si="3"/>
+        <v>118919</v>
+      </c>
+      <c r="M14" s="6">
+        <f t="shared" si="3"/>
+        <v>1784</v>
+      </c>
+      <c r="N14" s="6">
+        <f t="shared" si="3"/>
+        <v>791</v>
+      </c>
+    </row>
+    <row r="15" spans="2:14" ht="23" x14ac:dyDescent="0.35">
+      <c r="D15" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="13"/>
+      <c r="F15" s="20">
+        <f>F14/40</f>
         <v>2749.7</v>
       </c>
-      <c r="H14" s="12">
-        <f>SUM(H7:H13)</f>
+      <c r="G15" s="20">
+        <f t="shared" ref="G15:N15" si="4">G14/40</f>
         <v>2000</v>
       </c>
-      <c r="I14" s="12">
-        <f t="shared" ref="I14:O14" si="4">SUM(I7:I13)</f>
+      <c r="H15" s="20">
+        <f t="shared" si="4"/>
         <v>900</v>
       </c>
-      <c r="J14" s="12">
+      <c r="I15" s="20">
         <f t="shared" si="4"/>
         <v>5649.7</v>
       </c>
-      <c r="K14" s="12">
+      <c r="J15" s="20">
         <f t="shared" si="4"/>
-        <v>2614.44</v>
-      </c>
-      <c r="L14" s="12">
+        <v>2721.3249999999998</v>
+      </c>
+      <c r="K15" s="20">
         <f t="shared" si="4"/>
-        <v>3035.26</v>
-      </c>
-      <c r="M14" s="12">
+        <v>2928.375</v>
+      </c>
+      <c r="L15" s="20">
         <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="N14" s="12">
+        <v>2972.9749999999999</v>
+      </c>
+      <c r="M15" s="20">
         <f t="shared" si="4"/>
-        <v>3035.26</v>
-      </c>
-      <c r="O14" s="12">
+        <v>44.6</v>
+      </c>
+      <c r="N15" s="20">
         <f t="shared" si="4"/>
-        <v>791</v>
-      </c>
-    </row>
-    <row r="15" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="K15" s="18"/>
-    </row>
-    <row r="16" spans="3:15" x14ac:dyDescent="0.35">
-      <c r="K16" s="18"/>
-    </row>
-    <row r="17" spans="11:11" x14ac:dyDescent="0.35">
-      <c r="K17" s="3"/>
+        <v>19.774999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="2:14" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D16" s="14" t="s">
+        <v>23</v>
+      </c>
+      <c r="E16" s="13"/>
+      <c r="F16" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" s="15"/>
+      <c r="H16" s="15"/>
+      <c r="I16" s="15"/>
+      <c r="J16" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="K16" s="17" t="s">
+        <v>15</v>
+      </c>
+      <c r="L16" s="17"/>
+      <c r="M16" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="N16" s="18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="8:11" x14ac:dyDescent="0.35">
+      <c r="J17" s="1"/>
+    </row>
+    <row r="19" spans="8:11" x14ac:dyDescent="0.35">
+      <c r="H19">
+        <v>114430</v>
+      </c>
+      <c r="I19">
+        <f>H19/40</f>
+        <v>2860.75</v>
+      </c>
+      <c r="K19">
+        <v>110380</v>
+      </c>
+    </row>
+    <row r="20" spans="8:11" x14ac:dyDescent="0.35">
+      <c r="H20">
+        <f>H19/40</f>
+        <v>2860.75</v>
+      </c>
+      <c r="I20">
+        <v>40537</v>
+      </c>
+      <c r="K20">
+        <f>K19/40</f>
+        <v>2759.5</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="D5:O5"/>
+  <mergeCells count="3">
+    <mergeCell ref="D5:N5"/>
+    <mergeCell ref="F16:I16"/>
+    <mergeCell ref="K16:L16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Pimary VS Secondary.xlsx
+++ b/Pimary VS Secondary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03C6DBA0-585F-4DD1-A31D-3D805183713D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E0C84A-418C-490B-BC90-47FCFDBF7E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{B13BB3DE-45F3-4A08-8C5B-C8EF34D5413B}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="25">
   <si>
     <t>PRODUCT</t>
   </si>
@@ -91,9 +91,6 @@
   </si>
   <si>
     <t xml:space="preserve">Monthly Sales &amp; Inventory Report </t>
-  </si>
-  <si>
-    <t>s</t>
   </si>
   <si>
     <t>Til 23rd</t>
@@ -189,30 +186,33 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="Book Antiqua"/>
-      <family val="1"/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <u/>
       <sz val="16"/>
       <color theme="1"/>
-      <name val="Book Antiqua"/>
-      <family val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="22"/>
       <color theme="1"/>
-      <name val="Book Antiqua"/>
-      <family val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Book Antiqua"/>
-      <family val="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="8">
@@ -286,7 +286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -313,49 +313,52 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="10" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -672,13 +675,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C4897FB-F3E4-4933-BDE3-BEDB17D2ED6F}">
-  <dimension ref="B5:N20"/>
+  <dimension ref="C5:N17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="4" max="4" width="44.54296875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="7.26953125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.7265625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.26953125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.6328125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="29.54296875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="17.81640625" bestFit="1" customWidth="1"/>
@@ -688,59 +691,59 @@
     <col min="14" max="14" width="13.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="2:14" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="D5" s="10" t="s">
+    <row r="5" spans="3:14" ht="18.5" x14ac:dyDescent="0.35">
+      <c r="D5" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="10"/>
-      <c r="F5" s="10"/>
-      <c r="G5" s="10"/>
-      <c r="H5" s="10"/>
-      <c r="I5" s="10"/>
-      <c r="J5" s="10"/>
-      <c r="K5" s="10"/>
-      <c r="L5" s="10"/>
-      <c r="M5" s="10"/>
-      <c r="N5" s="10"/>
-    </row>
-    <row r="6" spans="2:14" ht="30.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="E5" s="23"/>
+      <c r="F5" s="23"/>
+      <c r="G5" s="23"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="23"/>
+      <c r="J5" s="23"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="23"/>
+      <c r="M5" s="23"/>
+      <c r="N5" s="23"/>
+    </row>
+    <row r="6" spans="3:14" ht="30.5" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="C6" s="9"/>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="G6" s="19">
+      <c r="G6" s="18">
         <v>46029</v>
       </c>
-      <c r="H6" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="12" t="s">
+      <c r="H6" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="J6" s="12" t="s">
+      <c r="I6" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="J6" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="K6" s="12" t="s">
+      <c r="K6" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="L6" s="12" t="s">
+      <c r="L6" s="17" t="s">
         <v>13</v>
       </c>
-      <c r="M6" s="12" t="s">
+      <c r="M6" s="17" t="s">
         <v>12</v>
       </c>
-      <c r="N6" s="12" t="s">
+      <c r="N6" s="17" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:14" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="D7" s="12" t="s">
+    <row r="7" spans="3:14" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="D7" s="10" t="s">
         <v>3</v>
       </c>
       <c r="E7" s="2">
@@ -749,24 +752,24 @@
       <c r="F7" s="4">
         <v>9586</v>
       </c>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21">
+      <c r="G7" s="13"/>
+      <c r="H7" s="13">
         <f>300*40</f>
         <v>12000</v>
       </c>
-      <c r="I7" s="22">
+      <c r="I7" s="14">
         <f t="shared" ref="I7:I13" si="0">F7+G7+H7</f>
         <v>21586</v>
       </c>
       <c r="J7" s="5">
-        <v>11967</v>
-      </c>
-      <c r="K7" s="23">
+        <v>12387</v>
+      </c>
+      <c r="K7" s="15">
         <f>I7-J7</f>
-        <v>9619</v>
-      </c>
-      <c r="L7" s="24">
-        <v>9710</v>
+        <v>9199</v>
+      </c>
+      <c r="L7" s="16">
+        <v>9290</v>
       </c>
       <c r="M7" s="8">
         <f>L7-K7</f>
@@ -776,8 +779,8 @@
         <v>280</v>
       </c>
     </row>
-    <row r="8" spans="2:14" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="D8" s="12" t="s">
+    <row r="8" spans="3:14" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="D8" s="10" t="s">
         <v>4</v>
       </c>
       <c r="E8" s="2">
@@ -786,24 +789,24 @@
       <c r="F8" s="4">
         <v>10668</v>
       </c>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21">
+      <c r="G8" s="13"/>
+      <c r="H8" s="13">
         <f>200*40</f>
         <v>8000</v>
       </c>
-      <c r="I8" s="22">
+      <c r="I8" s="14">
         <f t="shared" si="0"/>
         <v>18668</v>
       </c>
       <c r="J8" s="5">
-        <v>11897</v>
-      </c>
-      <c r="K8" s="23">
+        <v>12397</v>
+      </c>
+      <c r="K8" s="15">
         <f t="shared" ref="K8:K13" si="1">I8-J8</f>
-        <v>6771</v>
-      </c>
-      <c r="L8" s="24">
-        <v>6906</v>
+        <v>6271</v>
+      </c>
+      <c r="L8" s="16">
+        <v>6406</v>
       </c>
       <c r="M8" s="8">
         <f t="shared" ref="M8:M13" si="2">L8-K8</f>
@@ -813,29 +816,26 @@
         <v>226</v>
       </c>
     </row>
-    <row r="9" spans="2:14" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="B9" t="s">
-        <v>22</v>
-      </c>
-      <c r="D9" s="12" t="s">
+    <row r="9" spans="3:14" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="D9" s="10" t="s">
         <v>5</v>
       </c>
       <c r="E9" s="2">
         <v>70</v>
       </c>
       <c r="F9" s="4"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="22">
+      <c r="G9" s="13"/>
+      <c r="H9" s="13"/>
+      <c r="I9" s="14">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="J9" s="5"/>
-      <c r="K9" s="23">
+      <c r="K9" s="15">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="L9" s="24"/>
+      <c r="L9" s="16"/>
       <c r="M9" s="8">
         <f t="shared" si="2"/>
         <v>0</v>
@@ -844,8 +844,8 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="2:14" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="D10" s="12" t="s">
+    <row r="10" spans="3:14" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="D10" s="10" t="s">
         <v>6</v>
       </c>
       <c r="E10" s="2">
@@ -854,24 +854,24 @@
       <c r="F10" s="4">
         <v>10905</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="13">
         <f>750*40</f>
         <v>30000</v>
       </c>
-      <c r="H10" s="21"/>
-      <c r="I10" s="22">
+      <c r="H10" s="13"/>
+      <c r="I10" s="14">
         <f t="shared" si="0"/>
         <v>40905</v>
       </c>
       <c r="J10" s="5">
-        <v>22476</v>
-      </c>
-      <c r="K10" s="23">
+        <v>22969</v>
+      </c>
+      <c r="K10" s="15">
         <f t="shared" si="1"/>
-        <v>18429</v>
-      </c>
-      <c r="L10" s="24">
-        <v>18826</v>
+        <v>17936</v>
+      </c>
+      <c r="L10" s="16">
+        <v>18333</v>
       </c>
       <c r="M10" s="8">
         <f t="shared" si="2"/>
@@ -881,8 +881,8 @@
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="2:14" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="D11" s="12" t="s">
+    <row r="11" spans="3:14" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="D11" s="10" t="s">
         <v>7</v>
       </c>
       <c r="E11" s="2">
@@ -891,24 +891,24 @@
       <c r="F11" s="4">
         <v>5595</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="13">
         <f>203*40</f>
         <v>8120</v>
       </c>
-      <c r="H11" s="21"/>
-      <c r="I11" s="22">
+      <c r="H11" s="13"/>
+      <c r="I11" s="14">
         <f t="shared" si="0"/>
         <v>13715</v>
       </c>
       <c r="J11" s="5">
-        <v>16904</v>
-      </c>
-      <c r="K11" s="23">
+        <v>17403</v>
+      </c>
+      <c r="K11" s="15">
         <f t="shared" si="1"/>
-        <v>-3189</v>
-      </c>
-      <c r="L11" s="24">
-        <v>12836</v>
+        <v>-3688</v>
+      </c>
+      <c r="L11" s="16">
+        <v>12337</v>
       </c>
       <c r="M11" s="8">
         <f t="shared" si="2"/>
@@ -918,8 +918,8 @@
         <v>139</v>
       </c>
     </row>
-    <row r="12" spans="2:14" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="D12" s="12" t="s">
+    <row r="12" spans="3:14" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="D12" s="10" t="s">
         <v>8</v>
       </c>
       <c r="E12" s="2">
@@ -928,27 +928,27 @@
       <c r="F12" s="4">
         <v>7110</v>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="13">
         <f>1047*40</f>
         <v>41880</v>
       </c>
-      <c r="H12" s="21">
+      <c r="H12" s="13">
         <f>400*40</f>
         <v>16000</v>
       </c>
-      <c r="I12" s="22">
+      <c r="I12" s="14">
         <f t="shared" si="0"/>
         <v>64990</v>
       </c>
       <c r="J12" s="5">
-        <v>27279</v>
-      </c>
-      <c r="K12" s="23">
+        <v>27937</v>
+      </c>
+      <c r="K12" s="15">
         <f t="shared" si="1"/>
-        <v>37711</v>
-      </c>
-      <c r="L12" s="24">
-        <v>22468</v>
+        <v>37053</v>
+      </c>
+      <c r="L12" s="16">
+        <v>21810</v>
       </c>
       <c r="M12" s="8">
         <f t="shared" si="2"/>
@@ -958,8 +958,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="D13" s="12" t="s">
+    <row r="13" spans="3:14" ht="23.5" x14ac:dyDescent="0.35">
+      <c r="D13" s="10" t="s">
         <v>9</v>
       </c>
       <c r="E13" s="2">
@@ -968,21 +968,21 @@
       <c r="F13" s="4">
         <v>66124</v>
       </c>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="22">
+      <c r="G13" s="13"/>
+      <c r="H13" s="13"/>
+      <c r="I13" s="14">
         <f t="shared" si="0"/>
         <v>66124</v>
       </c>
       <c r="J13" s="5">
-        <v>18330</v>
-      </c>
-      <c r="K13" s="23">
+        <v>18442</v>
+      </c>
+      <c r="K13" s="15">
         <f t="shared" si="1"/>
-        <v>47794</v>
-      </c>
-      <c r="L13" s="24">
-        <v>48173</v>
+        <v>47682</v>
+      </c>
+      <c r="L13" s="16">
+        <v>48061</v>
       </c>
       <c r="M13" s="8">
         <f t="shared" si="2"/>
@@ -992,11 +992,11 @@
         <v>23</v>
       </c>
     </row>
-    <row r="14" spans="2:14" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D14" s="12" t="s">
+    <row r="14" spans="3:14" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D14" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="E14" s="13"/>
+      <c r="E14" s="11"/>
       <c r="F14" s="3">
         <f>SUM(F7:F13)</f>
         <v>109988</v>
@@ -1015,15 +1015,15 @@
       </c>
       <c r="J14" s="6">
         <f t="shared" si="3"/>
-        <v>108853</v>
+        <v>111535</v>
       </c>
       <c r="K14" s="6">
         <f t="shared" si="3"/>
-        <v>117135</v>
+        <v>114453</v>
       </c>
       <c r="L14" s="6">
         <f t="shared" si="3"/>
-        <v>118919</v>
+        <v>116237</v>
       </c>
       <c r="M14" s="6">
         <f t="shared" si="3"/>
@@ -1034,100 +1034,75 @@
         <v>791</v>
       </c>
     </row>
-    <row r="15" spans="2:14" ht="23" x14ac:dyDescent="0.35">
-      <c r="D15" s="12" t="s">
+    <row r="15" spans="3:14" ht="23" x14ac:dyDescent="0.35">
+      <c r="D15" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="E15" s="13"/>
-      <c r="F15" s="20">
+      <c r="E15" s="11"/>
+      <c r="F15" s="12">
         <f>F14/40</f>
         <v>2749.7</v>
       </c>
-      <c r="G15" s="20">
+      <c r="G15" s="12">
         <f t="shared" ref="G15:N15" si="4">G14/40</f>
         <v>2000</v>
       </c>
-      <c r="H15" s="20">
+      <c r="H15" s="12">
         <f t="shared" si="4"/>
         <v>900</v>
       </c>
-      <c r="I15" s="20">
+      <c r="I15" s="12">
         <f t="shared" si="4"/>
         <v>5649.7</v>
       </c>
-      <c r="J15" s="20">
+      <c r="J15" s="12">
         <f t="shared" si="4"/>
-        <v>2721.3249999999998</v>
-      </c>
-      <c r="K15" s="20">
+        <v>2788.375</v>
+      </c>
+      <c r="K15" s="12">
         <f t="shared" si="4"/>
-        <v>2928.375</v>
-      </c>
-      <c r="L15" s="20">
+        <v>2861.3249999999998</v>
+      </c>
+      <c r="L15" s="12">
         <f t="shared" si="4"/>
-        <v>2972.9749999999999</v>
-      </c>
-      <c r="M15" s="20">
+        <v>2905.9250000000002</v>
+      </c>
+      <c r="M15" s="12">
         <f t="shared" si="4"/>
         <v>44.6</v>
       </c>
-      <c r="N15" s="20">
+      <c r="N15" s="12">
         <f t="shared" si="4"/>
         <v>19.774999999999999</v>
       </c>
     </row>
-    <row r="16" spans="2:14" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D16" s="14" t="s">
-        <v>23</v>
-      </c>
-      <c r="E16" s="13"/>
-      <c r="F16" s="15" t="s">
+    <row r="16" spans="3:14" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D16" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="E16" s="20"/>
+      <c r="F16" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="G16" s="15"/>
-      <c r="H16" s="15"/>
-      <c r="I16" s="15"/>
-      <c r="J16" s="16" t="s">
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="K16" s="17" t="s">
+      <c r="K16" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="L16" s="17"/>
-      <c r="M16" s="11" t="s">
+      <c r="L16" s="25"/>
+      <c r="M16" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="N16" s="18" t="s">
+      <c r="N16" s="22" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="8:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="10:10" x14ac:dyDescent="0.35">
       <c r="J17" s="1"/>
-    </row>
-    <row r="19" spans="8:11" x14ac:dyDescent="0.35">
-      <c r="H19">
-        <v>114430</v>
-      </c>
-      <c r="I19">
-        <f>H19/40</f>
-        <v>2860.75</v>
-      </c>
-      <c r="K19">
-        <v>110380</v>
-      </c>
-    </row>
-    <row r="20" spans="8:11" x14ac:dyDescent="0.35">
-      <c r="H20">
-        <f>H19/40</f>
-        <v>2860.75</v>
-      </c>
-      <c r="I20">
-        <v>40537</v>
-      </c>
-      <c r="K20">
-        <f>K19/40</f>
-        <v>2759.5</v>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/Pimary VS Secondary.xlsx
+++ b/Pimary VS Secondary.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\786\Desktop\Elite-Git\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E0C84A-418C-490B-BC90-47FCFDBF7E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3479619E-CDC9-4E45-B631-6662658BDBEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{B13BB3DE-45F3-4A08-8C5B-C8EF34D5413B}"/>
   </bookViews>
@@ -93,13 +93,13 @@
     <t xml:space="preserve">Monthly Sales &amp; Inventory Report </t>
   </si>
   <si>
-    <t>Til 23rd</t>
-  </si>
-  <si>
     <t>Total Primary WH</t>
   </si>
   <si>
     <t>18/7/26</t>
+  </si>
+  <si>
+    <t>Till 28 july</t>
   </si>
 </sst>
 </file>
@@ -721,10 +721,10 @@
         <v>46029</v>
       </c>
       <c r="H6" s="17" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I6" s="17" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J6" s="17" t="s">
         <v>2</v>
@@ -762,18 +762,18 @@
         <v>21586</v>
       </c>
       <c r="J7" s="5">
-        <v>12387</v>
+        <v>13365</v>
       </c>
       <c r="K7" s="15">
         <f>I7-J7</f>
-        <v>9199</v>
+        <v>8221</v>
       </c>
       <c r="L7" s="16">
-        <v>9290</v>
+        <v>8379</v>
       </c>
       <c r="M7" s="8">
         <f>L7-K7</f>
-        <v>91</v>
+        <v>158</v>
       </c>
       <c r="N7" s="7">
         <v>280</v>
@@ -799,18 +799,18 @@
         <v>18668</v>
       </c>
       <c r="J8" s="5">
-        <v>12397</v>
+        <v>13225</v>
       </c>
       <c r="K8" s="15">
         <f t="shared" ref="K8:K13" si="1">I8-J8</f>
-        <v>6271</v>
+        <v>5443</v>
       </c>
       <c r="L8" s="16">
-        <v>6406</v>
+        <v>5485</v>
       </c>
       <c r="M8" s="8">
         <f t="shared" ref="M8:M13" si="2">L8-K8</f>
-        <v>135</v>
+        <v>42</v>
       </c>
       <c r="N8" s="7">
         <v>226</v>
@@ -864,18 +864,18 @@
         <v>40905</v>
       </c>
       <c r="J10" s="5">
-        <v>22969</v>
+        <v>24378</v>
       </c>
       <c r="K10" s="15">
         <f t="shared" si="1"/>
-        <v>17936</v>
+        <v>16527</v>
       </c>
       <c r="L10" s="16">
-        <v>18333</v>
+        <v>16921</v>
       </c>
       <c r="M10" s="8">
         <f t="shared" si="2"/>
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="N10" s="7">
         <v>64</v>
@@ -901,18 +901,18 @@
         <v>13715</v>
       </c>
       <c r="J11" s="5">
-        <v>17403</v>
+        <v>18944</v>
       </c>
       <c r="K11" s="15">
         <f t="shared" si="1"/>
-        <v>-3688</v>
+        <v>-5229</v>
       </c>
       <c r="L11" s="16">
-        <v>12337</v>
+        <v>10797</v>
       </c>
       <c r="M11" s="8">
         <f t="shared" si="2"/>
-        <v>16025</v>
+        <v>16026</v>
       </c>
       <c r="N11" s="7">
         <v>139</v>
@@ -941,18 +941,18 @@
         <v>64990</v>
       </c>
       <c r="J12" s="5">
-        <v>27937</v>
+        <v>29424</v>
       </c>
       <c r="K12" s="15">
         <f t="shared" si="1"/>
-        <v>37053</v>
+        <v>35566</v>
       </c>
       <c r="L12" s="16">
-        <v>21810</v>
+        <v>20322</v>
       </c>
       <c r="M12" s="8">
         <f t="shared" si="2"/>
-        <v>-15243</v>
+        <v>-15244</v>
       </c>
       <c r="N12" s="7">
         <v>18</v>
@@ -975,18 +975,18 @@
         <v>66124</v>
       </c>
       <c r="J13" s="5">
-        <v>18442</v>
+        <v>19350</v>
       </c>
       <c r="K13" s="15">
         <f t="shared" si="1"/>
-        <v>47682</v>
+        <v>46774</v>
       </c>
       <c r="L13" s="16">
-        <v>48061</v>
+        <v>47139</v>
       </c>
       <c r="M13" s="8">
         <f t="shared" si="2"/>
-        <v>379</v>
+        <v>365</v>
       </c>
       <c r="N13" s="7">
         <v>23</v>
@@ -1015,19 +1015,19 @@
       </c>
       <c r="J14" s="6">
         <f t="shared" si="3"/>
-        <v>111535</v>
+        <v>118686</v>
       </c>
       <c r="K14" s="6">
         <f t="shared" si="3"/>
-        <v>114453</v>
+        <v>107302</v>
       </c>
       <c r="L14" s="6">
         <f t="shared" si="3"/>
-        <v>116237</v>
+        <v>109043</v>
       </c>
       <c r="M14" s="6">
         <f t="shared" si="3"/>
-        <v>1784</v>
+        <v>1741</v>
       </c>
       <c r="N14" s="6">
         <f t="shared" si="3"/>
@@ -1057,19 +1057,19 @@
       </c>
       <c r="J15" s="12">
         <f t="shared" si="4"/>
-        <v>2788.375</v>
+        <v>2967.15</v>
       </c>
       <c r="K15" s="12">
         <f t="shared" si="4"/>
-        <v>2861.3249999999998</v>
+        <v>2682.55</v>
       </c>
       <c r="L15" s="12">
         <f t="shared" si="4"/>
-        <v>2905.9250000000002</v>
+        <v>2726.0749999999998</v>
       </c>
       <c r="M15" s="12">
         <f t="shared" si="4"/>
-        <v>44.6</v>
+        <v>43.524999999999999</v>
       </c>
       <c r="N15" s="12">
         <f t="shared" si="4"/>
@@ -1078,7 +1078,7 @@
     </row>
     <row r="16" spans="3:14" ht="30.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D16" s="19" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="E16" s="20"/>
       <c r="F16" s="24" t="s">
